--- a/02_Basic_Excel_for_Data_Analytics/12_Formatting-data-in-Excel-sheet.xlsx
+++ b/02_Basic_Excel_for_Data_Analytics/12_Formatting-data-in-Excel-sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01 COURSES\Learn_Data_Analytics_by_CWH\02_Basic_Excel_for_Data_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83A6493-8C1B-4242-9C60-BC05FF53E153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4803F5B1-8C12-42B0-BDC2-596662792C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
